--- a/research/traditional_assets/database/data/greece/greece_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0532</v>
+        <v>0.3235</v>
       </c>
       <c r="E2">
-        <v>0.267</v>
+        <v>0.47</v>
       </c>
       <c r="G2">
-        <v>0.2129060579455663</v>
+        <v>0.4162210338680927</v>
       </c>
       <c r="H2">
-        <v>0.2129060579455663</v>
+        <v>0.4162210338680927</v>
       </c>
       <c r="I2">
-        <v>0.2932396839332749</v>
+        <v>0.382620320855615</v>
       </c>
       <c r="J2">
-        <v>0.2523003774101228</v>
+        <v>0.3033903972236466</v>
       </c>
       <c r="K2">
-        <v>2.104</v>
+        <v>3.386</v>
       </c>
       <c r="L2">
-        <v>0.2309043020193152</v>
+        <v>0.3017825311942959</v>
       </c>
       <c r="M2">
-        <v>1.26</v>
+        <v>2.952</v>
       </c>
       <c r="N2">
-        <v>0.04914196567862714</v>
+        <v>0.148565676899849</v>
       </c>
       <c r="O2">
-        <v>0.5988593155893536</v>
+        <v>0.87182516243355</v>
       </c>
       <c r="P2">
-        <v>1.185</v>
+        <v>2.854</v>
       </c>
       <c r="Q2">
-        <v>0.04621684867394696</v>
+        <v>0.1436336185203825</v>
       </c>
       <c r="R2">
-        <v>0.563212927756654</v>
+        <v>0.8428824571766096</v>
       </c>
       <c r="S2">
-        <v>0.07500000000000001</v>
+        <v>0.09800000000000017</v>
       </c>
       <c r="T2">
-        <v>0.05952380952380953</v>
+        <v>0.03319783197831984</v>
       </c>
       <c r="U2">
-        <v>3.73</v>
+        <v>4.609999999999999</v>
       </c>
       <c r="V2">
-        <v>0.1454758190327613</v>
+        <v>0.2320080523402113</v>
       </c>
       <c r="W2">
-        <v>0.1834728578338356</v>
+        <v>0.2661222339304531</v>
       </c>
       <c r="X2">
-        <v>0.07107642746003617</v>
+        <v>0.1261226481520729</v>
       </c>
       <c r="Y2">
-        <v>0.1123964303737995</v>
+        <v>0.1399995857783802</v>
       </c>
       <c r="Z2">
-        <v>0.7028152718858465</v>
+        <v>0.8831863979848866</v>
       </c>
       <c r="AA2">
-        <v>0.2425998297203684</v>
+        <v>0.3046993996491257</v>
       </c>
       <c r="AB2">
-        <v>0.06995331594278886</v>
+        <v>0.1117532844573196</v>
       </c>
       <c r="AC2">
-        <v>0.1726465137775796</v>
+        <v>0.1929461151918062</v>
       </c>
       <c r="AD2">
-        <v>0.784</v>
+        <v>4.91</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.784</v>
+        <v>4.91</v>
       </c>
       <c r="AG2">
-        <v>-2.946000000000001</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="AH2">
-        <v>0.02966999697244929</v>
+        <v>0.1981436642453591</v>
       </c>
       <c r="AI2">
-        <v>0.04770597541681879</v>
+        <v>0.2529623905203504</v>
       </c>
       <c r="AJ2">
-        <v>-0.1298140477659294</v>
+        <v>0.01487357461576602</v>
       </c>
       <c r="AK2">
-        <v>-0.2318954659949622</v>
+        <v>0.02027027027027032</v>
       </c>
       <c r="AL2">
-        <v>0.06900000000000001</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.064</v>
+        <v>0.02399999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.336480686695279</v>
+        <v>1.221393034825871</v>
       </c>
       <c r="AO2">
-        <v>38.72463768115942</v>
+        <v>51.10714285714286</v>
       </c>
       <c r="AP2">
-        <v>-1.264377682403434</v>
+        <v>0.07462686567164198</v>
       </c>
       <c r="AQ2">
-        <v>-41.75</v>
+        <v>178.8750000000001</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0532</v>
+        <v>0.141</v>
       </c>
       <c r="E3">
-        <v>0.267</v>
+        <v>0.5579999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2389162561576355</v>
+        <v>0.4533980582524271</v>
       </c>
       <c r="H3">
-        <v>0.2389162561576355</v>
+        <v>0.4533980582524271</v>
       </c>
       <c r="I3">
-        <v>0.2733990147783252</v>
+        <v>0.3796116504854369</v>
       </c>
       <c r="J3">
-        <v>0.1970603288337279</v>
+        <v>0.2837597087378641</v>
       </c>
       <c r="K3">
-        <v>1.67</v>
+        <v>3.08</v>
       </c>
       <c r="L3">
-        <v>0.2056650246305419</v>
+        <v>0.2990291262135922</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>2.659</v>
       </c>
       <c r="N3">
-        <v>0.05833333333333333</v>
+        <v>0.191294964028777</v>
       </c>
       <c r="O3">
-        <v>0.62874251497006</v>
+        <v>0.8633116883116884</v>
       </c>
       <c r="P3">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
-        <v>0.05833333333333333</v>
+        <v>0.1884892086330935</v>
       </c>
       <c r="R3">
-        <v>0.62874251497006</v>
+        <v>0.8506493506493507</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.03900000000000015</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01466716810831145</v>
       </c>
       <c r="U3">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="V3">
-        <v>0.07444444444444445</v>
+        <v>0.1107913669064748</v>
       </c>
       <c r="W3">
-        <v>0.316888045540797</v>
+        <v>0.5</v>
       </c>
       <c r="X3">
-        <v>0.07025044385884999</v>
+        <v>0.1134668222952394</v>
       </c>
       <c r="Y3">
-        <v>0.246637601681947</v>
+        <v>0.3865331777047606</v>
       </c>
       <c r="Z3">
-        <v>2.215552523874488</v>
+        <v>1.99767261442979</v>
       </c>
       <c r="AA3">
-        <v>0.4365975089031024</v>
+        <v>0.5668589992242048</v>
       </c>
       <c r="AB3">
-        <v>0.06971481038834564</v>
+        <v>0.1094261025048899</v>
       </c>
       <c r="AC3">
-        <v>0.3668826985147568</v>
+        <v>0.4574328967193149</v>
       </c>
       <c r="AD3">
-        <v>0.336</v>
+        <v>1.47</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.336</v>
+        <v>1.47</v>
       </c>
       <c r="AG3">
-        <v>-1.004</v>
+        <v>-0.07000000000000006</v>
       </c>
       <c r="AH3">
-        <v>0.01832460732984293</v>
+        <v>0.09564085881587507</v>
       </c>
       <c r="AI3">
-        <v>0.05172413793103448</v>
+        <v>0.1936758893280632</v>
       </c>
       <c r="AJ3">
-        <v>-0.05907272299364557</v>
+        <v>-0.00506146059291396</v>
       </c>
       <c r="AK3">
-        <v>-0.1947245927075252</v>
+        <v>-0.01157024793388431</v>
       </c>
       <c r="AL3">
-        <v>0.039</v>
+        <v>0.061</v>
       </c>
       <c r="AM3">
-        <v>-0.094</v>
+        <v>0.001000000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.144206008583691</v>
+        <v>0.3656716417910448</v>
       </c>
       <c r="AO3">
-        <v>56.92307692307693</v>
+        <v>64.09836065573771</v>
       </c>
       <c r="AP3">
-        <v>-0.430901287553648</v>
+        <v>-0.0174129353233831</v>
       </c>
       <c r="AQ3">
-        <v>-23.61702127659575</v>
+        <v>3909.999999999997</v>
       </c>
     </row>
     <row r="4">
@@ -855,6 +855,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.506</v>
+      </c>
+      <c r="E4">
+        <v>0.382</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -862,103 +868,103 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.4556451612903226</v>
+        <v>0.4163043478260869</v>
       </c>
       <c r="J4">
-        <v>0.4556451612903226</v>
+        <v>0.3490113162596784</v>
       </c>
       <c r="K4">
-        <v>0.434</v>
+        <v>0.306</v>
       </c>
       <c r="L4">
-        <v>0.4375</v>
+        <v>0.3326086956521739</v>
       </c>
       <c r="M4">
-        <v>0.21</v>
+        <v>0.293</v>
       </c>
       <c r="N4">
-        <v>0.0274869109947644</v>
+        <v>0.04907872696817421</v>
       </c>
       <c r="O4">
-        <v>0.4838709677419356</v>
+        <v>0.9575163398692812</v>
       </c>
       <c r="P4">
-        <v>0.135</v>
+        <v>0.234</v>
       </c>
       <c r="Q4">
-        <v>0.01767015706806283</v>
+        <v>0.03919597989949749</v>
       </c>
       <c r="R4">
-        <v>0.3110599078341014</v>
+        <v>0.7647058823529412</v>
       </c>
       <c r="S4">
-        <v>0.07500000000000001</v>
+        <v>0.05900000000000002</v>
       </c>
       <c r="T4">
-        <v>0.3571428571428572</v>
+        <v>0.2013651877133106</v>
       </c>
       <c r="U4">
-        <v>2.39</v>
+        <v>3.07</v>
       </c>
       <c r="V4">
-        <v>0.3128272251308901</v>
+        <v>0.5142378559463987</v>
       </c>
       <c r="W4">
-        <v>0.05005767012687428</v>
+        <v>0.03224446786090621</v>
       </c>
       <c r="X4">
-        <v>0.07190241106122235</v>
+        <v>0.1387784740089064</v>
       </c>
       <c r="Y4">
-        <v>-0.02184474093434807</v>
+        <v>-0.1065340061480002</v>
       </c>
       <c r="Z4">
-        <v>0.1066666666666667</v>
+        <v>0.1218865924748278</v>
       </c>
       <c r="AA4">
-        <v>0.04860215053763441</v>
+        <v>0.04253980007404665</v>
       </c>
       <c r="AB4">
-        <v>0.0701918214972321</v>
+        <v>0.1140804664097492</v>
       </c>
       <c r="AC4">
-        <v>-0.02158967095959769</v>
+        <v>-0.07154066633570255</v>
       </c>
       <c r="AD4">
-        <v>0.448</v>
+        <v>3.44</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.448</v>
+        <v>3.44</v>
       </c>
       <c r="AG4">
-        <v>-1.942</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.05539070227497528</v>
+        <v>0.3655685441020191</v>
       </c>
       <c r="AI4">
-        <v>0.04507949285570537</v>
+        <v>0.2910321489001692</v>
       </c>
       <c r="AJ4">
-        <v>-0.3408213408213409</v>
+        <v>0.05835962145110412</v>
       </c>
       <c r="AK4">
-        <v>-0.2572866984631691</v>
+        <v>0.04228571428571429</v>
       </c>
       <c r="AL4">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="AM4">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="AO4">
-        <v>15.06666666666667</v>
+        <v>16.65217391304348</v>
       </c>
       <c r="AQ4">
-        <v>15.06666666666667</v>
+        <v>16.65217391304348</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3235</v>
+        <v>-0.0129</v>
       </c>
       <c r="E2">
-        <v>0.47</v>
+        <v>-0.169</v>
       </c>
       <c r="G2">
-        <v>0.4162210338680927</v>
+        <v>0.1239751552795031</v>
       </c>
       <c r="H2">
-        <v>0.4162210338680927</v>
+        <v>0.1239751552795031</v>
       </c>
       <c r="I2">
-        <v>0.382620320855615</v>
+        <v>0.1403726708074534</v>
       </c>
       <c r="J2">
-        <v>0.3033903972236466</v>
+        <v>0.1102538744497377</v>
       </c>
       <c r="K2">
-        <v>3.386</v>
+        <v>0.805</v>
       </c>
       <c r="L2">
-        <v>0.3017825311942959</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="M2">
-        <v>2.952</v>
+        <v>0.927</v>
       </c>
       <c r="N2">
-        <v>0.148565676899849</v>
+        <v>0.04311627906976744</v>
       </c>
       <c r="O2">
-        <v>0.87182516243355</v>
+        <v>1.151552795031056</v>
       </c>
       <c r="P2">
-        <v>2.854</v>
+        <v>0.764</v>
       </c>
       <c r="Q2">
-        <v>0.1436336185203825</v>
+        <v>0.03553488372093024</v>
       </c>
       <c r="R2">
-        <v>0.8428824571766096</v>
+        <v>0.9490683229813665</v>
       </c>
       <c r="S2">
-        <v>0.09800000000000017</v>
+        <v>0.163</v>
       </c>
       <c r="T2">
-        <v>0.03319783197831984</v>
+        <v>0.1758360302049623</v>
       </c>
       <c r="U2">
-        <v>4.609999999999999</v>
+        <v>0.112</v>
       </c>
       <c r="V2">
-        <v>0.2320080523402113</v>
+        <v>0.005209302325581395</v>
       </c>
       <c r="W2">
-        <v>0.2661222339304531</v>
+        <v>0.1315359477124183</v>
       </c>
       <c r="X2">
-        <v>0.1261226481520729</v>
+        <v>0.0836846905782046</v>
       </c>
       <c r="Y2">
-        <v>0.1399995857783802</v>
+        <v>0.0478512571342137</v>
       </c>
       <c r="Z2">
-        <v>0.8831863979848866</v>
+        <v>1.330578512396694</v>
       </c>
       <c r="AA2">
-        <v>0.3046993996491257</v>
+        <v>0.1467014362513039</v>
       </c>
       <c r="AB2">
-        <v>0.1117532844573196</v>
+        <v>0.0816423761659151</v>
       </c>
       <c r="AC2">
-        <v>0.1929461151918062</v>
+        <v>0.06505906008538875</v>
       </c>
       <c r="AD2">
-        <v>4.91</v>
+        <v>1.74</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG2">
-        <v>0.3000000000000007</v>
+        <v>1.628</v>
       </c>
       <c r="AH2">
-        <v>0.1981436642453591</v>
+        <v>0.07487091222030981</v>
       </c>
       <c r="AI2">
-        <v>0.2529623905203504</v>
+        <v>0.2103990326481258</v>
       </c>
       <c r="AJ2">
-        <v>0.01487357461576602</v>
+        <v>0.07039086821169145</v>
       </c>
       <c r="AK2">
-        <v>0.02027027027027032</v>
+        <v>0.1995587153714146</v>
       </c>
       <c r="AL2">
-        <v>0.08399999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="AM2">
-        <v>0.02399999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="AN2">
-        <v>1.221393034825871</v>
+        <v>1.5</v>
       </c>
       <c r="AO2">
-        <v>51.10714285714286</v>
+        <v>4.650205761316872</v>
       </c>
       <c r="AP2">
-        <v>0.07462686567164198</v>
+        <v>1.403448275862069</v>
       </c>
       <c r="AQ2">
-        <v>178.8750000000001</v>
+        <v>10.97087378640777</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alpha Trust Mutual Fund and Alternative Investment Fund Management S.A. (ATSE:ATRUST)</t>
+          <t>Alpha Trust Holdings S.A. (ATSE:ATRUST)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,249 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.141</v>
+        <v>-0.0129</v>
       </c>
       <c r="E3">
-        <v>0.5579999999999999</v>
+        <v>-0.169</v>
       </c>
       <c r="G3">
-        <v>0.4533980582524271</v>
+        <v>0.1239751552795031</v>
       </c>
       <c r="H3">
-        <v>0.4533980582524271</v>
+        <v>0.1239751552795031</v>
       </c>
       <c r="I3">
-        <v>0.3796116504854369</v>
+        <v>0.1403726708074534</v>
       </c>
       <c r="J3">
-        <v>0.2837597087378641</v>
+        <v>0.1102538744497377</v>
       </c>
       <c r="K3">
-        <v>3.08</v>
+        <v>0.805</v>
       </c>
       <c r="L3">
-        <v>0.2990291262135922</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="M3">
-        <v>2.659</v>
+        <v>0.927</v>
       </c>
       <c r="N3">
-        <v>0.191294964028777</v>
+        <v>0.04311627906976744</v>
       </c>
       <c r="O3">
-        <v>0.8633116883116884</v>
+        <v>1.151552795031056</v>
       </c>
       <c r="P3">
-        <v>2.62</v>
+        <v>0.764</v>
       </c>
       <c r="Q3">
-        <v>0.1884892086330935</v>
+        <v>0.03553488372093024</v>
       </c>
       <c r="R3">
-        <v>0.8506493506493507</v>
+        <v>0.9490683229813665</v>
       </c>
       <c r="S3">
-        <v>0.03900000000000015</v>
+        <v>0.163</v>
       </c>
       <c r="T3">
-        <v>0.01466716810831145</v>
+        <v>0.1758360302049623</v>
       </c>
       <c r="U3">
-        <v>1.54</v>
+        <v>0.112</v>
       </c>
       <c r="V3">
-        <v>0.1107913669064748</v>
+        <v>0.005209302325581395</v>
       </c>
       <c r="W3">
-        <v>0.5</v>
+        <v>0.1315359477124183</v>
       </c>
       <c r="X3">
-        <v>0.1134668222952394</v>
+        <v>0.0836846905782046</v>
       </c>
       <c r="Y3">
-        <v>0.3865331777047606</v>
+        <v>0.0478512571342137</v>
       </c>
       <c r="Z3">
-        <v>1.99767261442979</v>
+        <v>1.330578512396694</v>
       </c>
       <c r="AA3">
-        <v>0.5668589992242048</v>
+        <v>0.1467014362513039</v>
       </c>
       <c r="AB3">
-        <v>0.1094261025048899</v>
+        <v>0.0816423761659151</v>
       </c>
       <c r="AC3">
-        <v>0.4574328967193149</v>
+        <v>0.06505906008538875</v>
       </c>
       <c r="AD3">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AG3">
-        <v>-0.07000000000000006</v>
+        <v>1.628</v>
       </c>
       <c r="AH3">
-        <v>0.09564085881587507</v>
+        <v>0.07487091222030981</v>
       </c>
       <c r="AI3">
-        <v>0.1936758893280632</v>
+        <v>0.2103990326481258</v>
       </c>
       <c r="AJ3">
-        <v>-0.00506146059291396</v>
+        <v>0.07039086821169145</v>
       </c>
       <c r="AK3">
-        <v>-0.01157024793388431</v>
+        <v>0.1995587153714146</v>
       </c>
       <c r="AL3">
-        <v>0.061</v>
+        <v>0.243</v>
       </c>
       <c r="AM3">
-        <v>0.001000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="AN3">
-        <v>0.3656716417910448</v>
+        <v>1.5</v>
       </c>
       <c r="AO3">
-        <v>64.09836065573771</v>
+        <v>4.650205761316872</v>
       </c>
       <c r="AP3">
-        <v>-0.0174129353233831</v>
+        <v>1.403448275862069</v>
       </c>
       <c r="AQ3">
-        <v>3909.999999999997</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cnl Capital E.K.E.S. - AIFM (ATSE:CNLCAP)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.506</v>
-      </c>
-      <c r="E4">
-        <v>0.382</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0.4163043478260869</v>
-      </c>
-      <c r="J4">
-        <v>0.3490113162596784</v>
-      </c>
-      <c r="K4">
-        <v>0.306</v>
-      </c>
-      <c r="L4">
-        <v>0.3326086956521739</v>
-      </c>
-      <c r="M4">
-        <v>0.293</v>
-      </c>
-      <c r="N4">
-        <v>0.04907872696817421</v>
-      </c>
-      <c r="O4">
-        <v>0.9575163398692812</v>
-      </c>
-      <c r="P4">
-        <v>0.234</v>
-      </c>
-      <c r="Q4">
-        <v>0.03919597989949749</v>
-      </c>
-      <c r="R4">
-        <v>0.7647058823529412</v>
-      </c>
-      <c r="S4">
-        <v>0.05900000000000002</v>
-      </c>
-      <c r="T4">
-        <v>0.2013651877133106</v>
-      </c>
-      <c r="U4">
-        <v>3.07</v>
-      </c>
-      <c r="V4">
-        <v>0.5142378559463987</v>
-      </c>
-      <c r="W4">
-        <v>0.03224446786090621</v>
-      </c>
-      <c r="X4">
-        <v>0.1387784740089064</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1065340061480002</v>
-      </c>
-      <c r="Z4">
-        <v>0.1218865924748278</v>
-      </c>
-      <c r="AA4">
-        <v>0.04253980007404665</v>
-      </c>
-      <c r="AB4">
-        <v>0.1140804664097492</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07154066633570255</v>
-      </c>
-      <c r="AD4">
-        <v>3.44</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>3.44</v>
-      </c>
-      <c r="AG4">
-        <v>0.3700000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>0.3655685441020191</v>
-      </c>
-      <c r="AI4">
-        <v>0.2910321489001692</v>
-      </c>
-      <c r="AJ4">
-        <v>0.05835962145110412</v>
-      </c>
-      <c r="AK4">
-        <v>0.04228571428571429</v>
-      </c>
-      <c r="AL4">
-        <v>0.023</v>
-      </c>
-      <c r="AM4">
-        <v>0.023</v>
-      </c>
-      <c r="AO4">
-        <v>16.65217391304348</v>
-      </c>
-      <c r="AQ4">
-        <v>16.65217391304348</v>
+        <v>10.97087378640777</v>
       </c>
     </row>
   </sheetData>
